--- a/outputs/week2_excel/920116_星图测控_三表抽取.xlsx
+++ b/outputs/week2_excel/920116_星图测控_三表抽取.xlsx
@@ -2299,7 +2299,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>张松满</t>
+          <t>孙国敏</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -2317,7 +2317,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2337,7 +2341,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>孙国敏</t>
+          <t>张松满</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
@@ -2355,11 +2359,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
+      <c r="L35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>东方富海（上海）创业投资企业（有限合伙）</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -2459,15 +2459,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>深圳市云汉电子有限公司</t>
+          <t>东方富海（上海）创业投资企业（有限合伙）</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
@@ -2479,7 +2475,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2539,11 +2535,15 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>深圳市云汉电子有限公司</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
@@ -2555,7 +2555,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>东方富海（上海）创业投资企业（有限合伙）</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2615,7 +2615,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>东方富海（上海）创业投资企业（有限合伙）</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -2745,7 +2745,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -2859,7 +2859,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2881,11 +2881,15 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
@@ -2957,15 +2961,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
@@ -2999,7 +2999,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -3015,7 +3015,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -3113,7 +3113,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>曾烨</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>曾烨</t>
+          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -3357,7 +3357,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3417,7 +3417,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -3455,7 +3455,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3493,7 +3493,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3531,11 +3531,15 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
@@ -3547,7 +3551,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3569,13 +3573,13 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>7412.0</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
@@ -3611,13 +3615,13 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -3653,13 +3657,13 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>7412.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -3737,15 +3741,11 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>204.0</t>
-        </is>
-      </c>
+      <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
@@ -3757,7 +3757,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3821,15 +3821,11 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>厦门西堤股权投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>5000.0</t>
-        </is>
-      </c>
+      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
@@ -3841,7 +3837,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3863,11 +3859,15 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>厦门西堤股权投资合伙企业（有限合伙）</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>5000.0</t>
+        </is>
+      </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
@@ -3879,7 +3879,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3939,7 +3939,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
@@ -3977,11 +3977,15 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>昆山谷捷金属制品有限公司</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
@@ -3993,7 +3997,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4019,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -4053,15 +4057,11 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>昆山谷捷金属制品有限公司</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
@@ -4073,7 +4073,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4095,7 +4095,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -4163,7 +4163,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
@@ -4197,7 +4197,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -4251,7 +4251,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4273,7 +4273,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
@@ -4289,7 +4289,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4349,7 +4349,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
@@ -4429,11 +4429,15 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>10377.0</t>
+        </is>
+      </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
@@ -4445,7 +4449,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4467,15 +4471,11 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>10377.0</t>
-        </is>
-      </c>
+      <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr"/>
@@ -4487,7 +4487,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
@@ -4547,7 +4547,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
@@ -4585,7 +4585,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
@@ -4623,15 +4623,11 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2124.81</t>
-        </is>
-      </c>
+      <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
@@ -4641,7 +4637,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4661,11 +4661,15 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2124.81</t>
+        </is>
+      </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
@@ -4675,11 +4679,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -5387,22 +5387,14 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
+          <t>友升太平洋(美国)投资有限公司</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+      <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
@@ -5411,7 +5403,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5433,20 +5425,20 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+          <t>罗世兵</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="J111" t="inlineStr"/>
@@ -5479,14 +5471,22 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>上海市青浦县徐泾乡工业公司</t>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr"/>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5517,20 +5517,20 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>罗世兵</t>
+          <t>上海泽升贸易有限公司</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="J113" t="inlineStr"/>
@@ -5563,14 +5563,22 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>友升太平洋(美国)投资有限公司</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr"/>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr"/>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
         <is>
@@ -5579,7 +5587,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5601,22 +5609,14 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+          <t>上海市青浦县徐泾乡工业公司</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>1020.0</t>
-        </is>
-      </c>
+      <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>1020.0</t>
-        </is>
-      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5647,26 +5647,22 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>8976.0</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>17952.0</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
@@ -5675,7 +5671,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5697,22 +5693,26 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr"/>
+          <t>罗世兵</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>204.0</t>
+        </is>
+      </c>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
+          <t>204.0</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>408.0</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5793,22 +5793,26 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr"/>
+          <t>上海泽升贸易有限公司</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
+          <t>8976.0</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>17952.0</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
@@ -5817,7 +5821,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5839,26 +5843,22 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>罗世兵</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>204.0</t>
-        </is>
-      </c>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>204.0</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>408.0</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
@@ -5867,7 +5867,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5889,22 +5889,26 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr"/>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr"/>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
+          <t>1020.0</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>2040.0</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
@@ -5913,7 +5917,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5935,26 +5939,22 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>1020.0</t>
-        </is>
-      </c>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
-          <t>1020.0</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>2040.0</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5985,22 +5985,30 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr"/>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>7000.0</t>
+        </is>
+      </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>89.2</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>89.2</t>
-        </is>
-      </c>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>1680.0</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
@@ -6009,7 +6017,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6031,20 +6039,20 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>上海联炻企业管理中心(有限合伙)</t>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>86.5984</t>
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>86.5984</t>
         </is>
       </c>
       <c r="J124" t="inlineStr"/>
@@ -6077,20 +6085,20 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
+          <t>深圳市达晨财智创业投资管理有限公司</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
-          <t>86.5984</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
-          <t>86.5984</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="J125" t="inlineStr"/>
@@ -6123,22 +6131,30 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>深圳市达晨财智创业投资管理有限公司</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr"/>
-      <c r="F126" t="inlineStr"/>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>3000.0</t>
+        </is>
+      </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>29.7333</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr"/>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>29.7333</t>
-        </is>
-      </c>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>720.0</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
@@ -6147,7 +6163,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6169,20 +6185,20 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>10.1093</t>
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>10.1093</t>
         </is>
       </c>
       <c r="J127" t="inlineStr"/>
@@ -6215,27 +6231,27 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>7000.0</t>
+          <t>1500.0</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>1680.0</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -6269,20 +6285,20 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J129" t="inlineStr"/>
@@ -6315,20 +6331,20 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr">
         <is>
-          <t>59.4667</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="J130" t="inlineStr"/>
@@ -6361,20 +6377,20 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
+          <t>上海联炻企业管理中心(有限合伙)</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J131" t="inlineStr"/>
@@ -6407,30 +6423,22 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>1500.0</t>
-        </is>
-      </c>
+          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
+          <t>59.4667</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>59.4667</t>
+        </is>
+      </c>
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
@@ -6439,7 +6447,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6461,20 +6469,20 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="J133" t="inlineStr"/>
@@ -6553,30 +6561,22 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>720.0</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr"/>
+          <t>51.959</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>51.959</t>
+        </is>
+      </c>
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7457,7 +7457,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>周乃鼎</t>
+          <t>黄学英</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
@@ -7473,7 +7473,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7495,7 +7495,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>黄学英</t>
+          <t>华泰大健康一号</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
@@ -7533,7 +7533,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>周金清</t>
+          <t>复星惟盈</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
@@ -7571,7 +7571,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>国寿疌泉</t>
+          <t>陆民</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
@@ -7585,11 +7585,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L156" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -7609,7 +7605,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>陆民</t>
+          <t>黄学英/刘鸿雁</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -7623,7 +7619,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L157" t="inlineStr"/>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>退出</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -7643,7 +7643,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Cheer Rise Consultants Limited</t>
+          <t>周乃鼎</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -7681,7 +7681,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>复星惟盈</t>
+          <t>国寿疌泉</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -7719,7 +7719,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>高新同华</t>
+          <t>史建伟</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
@@ -7735,7 +7735,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7757,7 +7757,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>苏州贤达</t>
+          <t>高新同华</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -7795,7 +7795,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>黄学英/刘鸿雁</t>
+          <t>Cheer Rise Consultants Limited</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
@@ -7833,7 +7833,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>华泰大健康一号</t>
+          <t>周金清</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -7871,7 +7871,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>史建伟</t>
+          <t>苏州贤达</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -7887,7 +7887,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7909,7 +7909,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>深圳中证投资有限责任公司</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -7985,7 +7985,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>深圳市伊敦传媒投资基金合伙企业（有限合伙）</t>
+          <t>厦门富凯海创投资管理有限责任公司</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
@@ -8023,7 +8023,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
@@ -8039,7 +8039,7 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8099,7 +8099,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>厦门富凯海创投资管理有限责任公司</t>
+          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
@@ -8137,7 +8137,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>深圳中证投资有限责任公司</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
@@ -8153,7 +8153,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8175,7 +8175,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
+          <t>深圳市伊敦传媒投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
@@ -8213,7 +8213,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
@@ -8251,15 +8251,11 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F174" t="inlineStr"/>
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr"/>
@@ -8269,7 +8265,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L174" t="inlineStr"/>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -8327,11 +8327,15 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
-      <c r="F176" t="inlineStr"/>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G176" t="inlineStr"/>
       <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr"/>
@@ -8341,11 +8345,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L176" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
@@ -8517,7 +8517,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
@@ -8643,7 +8643,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>朱绶青</t>
+          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
@@ -8659,7 +8659,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8719,7 +8719,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
+          <t>朱绶青</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8757,13 +8757,13 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>四方股份</t>
+          <t>牛威(罗永红代持)</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr">
         <is>
-          <t>1200.0</t>
+          <t>400.0</t>
         </is>
       </c>
       <c r="G187" t="inlineStr"/>
@@ -8917,13 +8917,13 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>牛威(罗永红代持)</t>
+          <t>四方股份</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr">
         <is>
-          <t>400.0</t>
+          <t>1200.0</t>
         </is>
       </c>
       <c r="G191" t="inlineStr"/>
@@ -8959,18 +8959,22 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>策星九天</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G192" t="inlineStr"/>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
       <c r="H192" t="inlineStr"/>
-      <c r="I192" t="inlineStr"/>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr">
         <is>
@@ -8979,7 +8983,7 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9001,22 +9005,18 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>策星揽月</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
-      <c r="F193" t="inlineStr"/>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>412.5</t>
-        </is>
-      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr"/>
       <c r="H193" t="inlineStr"/>
-      <c r="I193" t="inlineStr">
-        <is>
-          <t>412.5</t>
-        </is>
-      </c>
+      <c r="I193" t="inlineStr"/>
       <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr">
         <is>
@@ -9025,7 +9025,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -9047,20 +9047,20 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>策星九天</t>
+          <t>幸福一期</t>
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr"/>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2345.0781</t>
+          <t>917.4219</t>
         </is>
       </c>
       <c r="H194" t="inlineStr"/>
       <c r="I194" t="inlineStr">
         <is>
-          <t>2345.0781</t>
+          <t>917.4219</t>
         </is>
       </c>
       <c r="J194" t="inlineStr"/>
@@ -9093,20 +9093,20 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>幸福二期</t>
+          <t>策星逐日</t>
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr"/>
       <c r="G195" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="H195" t="inlineStr"/>
       <c r="I195" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="J195" t="inlineStr"/>
@@ -9139,20 +9139,20 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>幸福一期</t>
+          <t>策星银河</t>
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr"/>
       <c r="G196" t="inlineStr">
         <is>
-          <t>917.4219</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="H196" t="inlineStr"/>
       <c r="I196" t="inlineStr">
         <is>
-          <t>917.4219</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="J196" t="inlineStr"/>
@@ -9231,20 +9231,20 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>策星逐日</t>
+          <t>幸福二期</t>
         </is>
       </c>
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr"/>
       <c r="G198" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>300.0</t>
         </is>
       </c>
       <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>300.0</t>
         </is>
       </c>
       <c r="J198" t="inlineStr"/>
@@ -9277,18 +9277,22 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>吴功友</t>
+          <t>策星揽月</t>
         </is>
       </c>
       <c r="E199" t="inlineStr"/>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G199" t="inlineStr"/>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
       <c r="H199" t="inlineStr"/>
-      <c r="I199" t="inlineStr"/>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
       <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr">
         <is>
@@ -9297,7 +9301,7 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9319,22 +9323,18 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>策星银河</t>
+          <t>吴功友</t>
         </is>
       </c>
       <c r="E200" t="inlineStr"/>
-      <c r="F200" t="inlineStr"/>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr"/>
       <c r="H200" t="inlineStr"/>
-      <c r="I200" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
+      <c r="I200" t="inlineStr"/>
       <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -9714,7 +9714,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>生成时间: 2026-06-12T15:16:11.130280</t>
+          <t>生成时间: 2026-06-12T16:09:12.799759</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/920116_星图测控_三表抽取.xlsx
+++ b/outputs/week2_excel/920116_星图测控_三表抽取.xlsx
@@ -1637,7 +1637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L211"/>
+  <dimension ref="A1:L143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2421,7 +2421,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>东方富海（上海）创业投资企业（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>东方富海（上海）创业投资企业（有限合伙）</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -2745,7 +2745,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2881,7 +2881,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -2897,7 +2897,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2919,7 +2919,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>曾烨</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -2935,7 +2935,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2957,7 +2957,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2995,11 +2995,15 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
@@ -3033,7 +3037,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -3049,7 +3053,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3071,15 +3075,11 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
@@ -3113,7 +3113,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>曾烨</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -3167,7 +3167,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>曾烨</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -3379,7 +3379,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -3417,7 +3417,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -3455,7 +3455,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -3493,7 +3493,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>曾烨</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3531,13 +3531,13 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1000.0</t>
+          <t>1800.0</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -3573,13 +3573,13 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>1584.0</t>
+          <t>7412.0</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
@@ -3657,13 +3657,13 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>1000.0</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -3699,15 +3699,11 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+      <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
@@ -3719,7 +3715,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3741,11 +3737,15 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>1584.0</t>
+        </is>
+      </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
@@ -3757,7 +3757,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3779,13 +3779,13 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>7412.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -3821,11 +3821,15 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>厦门西堤股权投资合伙企业（有限合伙）</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>5000.0</t>
+        </is>
+      </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
@@ -3837,7 +3841,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3897,15 +3901,11 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>厦门西堤股权投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>5000.0</t>
-        </is>
-      </c>
+      <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
@@ -3917,7 +3917,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3939,7 +3939,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
@@ -4015,15 +4015,11 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>昆山谷捷金属制品有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
@@ -4035,7 +4031,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4057,11 +4053,15 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>昆山谷捷金属制品有限公司</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
@@ -4073,7 +4073,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4095,7 +4095,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -4163,7 +4163,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
@@ -4197,7 +4197,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -4213,7 +4213,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -4251,7 +4251,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4273,7 +4273,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
@@ -4289,7 +4289,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4311,7 +4311,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -4327,7 +4327,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4349,7 +4349,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
@@ -4425,13 +4425,13 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>10377.0</t>
+          <t>1153.0</t>
         </is>
       </c>
       <c r="G89" t="inlineStr"/>
@@ -4467,13 +4467,13 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>1153.0</t>
+          <t>10377.0</t>
         </is>
       </c>
       <c r="G90" t="inlineStr"/>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
@@ -4547,15 +4547,11 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2124.81</t>
-        </is>
-      </c>
+      <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr"/>
@@ -4565,7 +4561,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr"/>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4623,11 +4623,15 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2124.81</t>
+        </is>
+      </c>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
@@ -4637,11 +4641,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>SAIC TECHNOLOGIES FUND II, LLC</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
@@ -4699,7 +4699,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -4722,42 +4722,30 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr"/>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>6999.972</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>7000.0</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>-0.028</t>
-        </is>
-      </c>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4765,49 +4753,37 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr"/>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>2999.988</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>-0.012</t>
-        </is>
-      </c>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4815,49 +4791,37 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr"/>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>1499.994</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>1500.0</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>-0.006</t>
-        </is>
-      </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4865,49 +4829,37 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr"/>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
+          <t>厦门富凯海创投资管理有限责任公司</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>297.3333</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>10000.0027</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>10000.0</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>0.0027</t>
-        </is>
-      </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4915,49 +4867,37 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr"/>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>上海联炻企业管理中心(有限合伙)</t>
+          <t>深圳市伊敦传媒投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>297.3333</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>10000.0027</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>10000.0</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>0.0027</t>
-        </is>
-      </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -4965,49 +4905,37 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr"/>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>148.6667</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>5000.0031</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>5000.0</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>0.0031</t>
-        </is>
-      </c>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5015,49 +4943,37 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr"/>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
+          <t>深圳中证投资有限责任公司</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>89.2</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>3000.0012</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>0.0012</t>
-        </is>
-      </c>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5065,49 +4981,37 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr"/>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
+          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>86.5984</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>2912.5034</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>2912.5</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>0.0034</t>
-        </is>
-      </c>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5115,49 +5019,37 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr"/>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2015-07-09</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
+          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>59.4667</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>2000.0019</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>2000.0</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>0.0019</t>
-        </is>
-      </c>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5165,99 +5057,75 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr"/>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>51.959</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>1747.5007</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>1747.5</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>0.0007</t>
-        </is>
-      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="L106" t="inlineStr">
-        <is>
-          <t>price×shares vs amount diff=0.0%</t>
-        </is>
-      </c>
+      <c r="L106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr"/>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>29.7333</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>999.9993</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>-0.0007</t>
-        </is>
-      </c>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5265,49 +5133,37 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr"/>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>深圳市达晨财智创业投资管理有限公司</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>29.7333</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>999.9993</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>-0.0007</t>
-        </is>
-      </c>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5315,49 +5171,37 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr"/>
+          <t>688775_影石创新</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2015-07-09</t>
+        </is>
+      </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>10.1093</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>339.999</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>340.0</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>-0.001</t>
-        </is>
-      </c>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5365,44 +5209,36 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>price×shares vs amount diff=0.0%</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>1992-12-04</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2023-03-24</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>1020.0</t>
-        </is>
-      </c>
+      <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>1020.0</t>
-        </is>
-      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
@@ -5411,44 +5247,36 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>1992-12-04</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2023-03-24</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+      <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
@@ -5457,29 +5285,29 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>1992-12-04</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2023-03-24</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>友升太平洋(美国)投资有限公司</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
@@ -5502,22 +5330,22 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>1992-12-04</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2023-03-24</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>上海市青浦县徐泾乡工业公司</t>
+          <t>汇智同裕（深圳）投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
@@ -5533,44 +5361,36 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
+          <t>688775_影石创新</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>1992-12-04</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2023-03-24</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+      <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
         <is>
@@ -5579,45 +5399,49 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>1992-12-04</t>
-        </is>
-      </c>
+          <t>920100_三协电机</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2023-09-06</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>罗世兵</t>
+          <t>盛祎等15名自然人</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>204.0</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr"/>
+          <t>321.5</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>1739.315</t>
+        </is>
+      </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>204.0</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr"/>
+          <t>1723.09</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>16.225</t>
+        </is>
+      </c>
       <c r="K115" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5625,47 +5449,35 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>price×shares vs amount diff=0.9%</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
+          <t>920100_三协电机</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2002-11-07</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-08-09</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>1020.0</t>
-        </is>
-      </c>
+          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>1020.0</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>2040.0</t>
-        </is>
-      </c>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
@@ -5675,47 +5487,35 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
+          <t>920100_三协电机</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2002-11-07</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-08-09</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+          <t>盛祎</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>17952.0</t>
-        </is>
-      </c>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr">
@@ -5732,37 +5532,29 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
+          <t>920100_三协电机</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2002-11-07</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2022-08-09</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+          <t>朱绶青</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
+      <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
         <is>
@@ -5771,44 +5563,40 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
+          <t>920116_星图测控</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2016-12-14</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2017-10-25</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+          <t>四方股份</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>1200.0</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
@@ -5817,47 +5605,35 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
+          <t>920116_星图测控</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2016-12-14</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2017-10-25</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+          <t>牛威</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>3600.0</t>
-        </is>
-      </c>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
@@ -5867,44 +5643,36 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
+          <t>920116_星图测控</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2016-12-14</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2017-10-25</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+          <t>吴功友</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
+      <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr"/>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
+      <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
@@ -5920,40 +5688,32 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
+          <t>920116_星图测控</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2016-12-14</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2017-10-25</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>罗世兵</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>204.0</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>204.0</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>408.0</t>
-        </is>
-      </c>
+          <t>牛威(罗永红代持)</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
@@ -5970,37 +5730,33 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
+          <t>920116_星图测控</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2016-12-14</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2017-10-25</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
+          <t>吴功友(王金林代持)</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>59.4667</t>
-        </is>
-      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>59.4667</t>
-        </is>
-      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
@@ -6009,42 +5765,42 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
+          <t>920116_星图测控</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2017-10-25</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
+          <t>策星银河</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>86.5984</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
-          <t>86.5984</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="J124" t="inlineStr"/>
@@ -6062,37 +5818,33 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
+          <t>920116_星图测控</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2017-10-25</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>深圳市达晨财智创业投资管理有限公司</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>29.7333</t>
-        </is>
-      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr"/>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>29.7333</t>
-        </is>
-      </c>
+      <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr">
         <is>
@@ -6101,52 +5853,44 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
+          <t>920116_星图测控</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2017-10-25</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>3000.0</t>
-        </is>
-      </c>
+          <t>幸福二期</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>720.0</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
@@ -6155,52 +5899,44 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
+          <t>920116_星图测控</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2017-10-25</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>1500.0</t>
-        </is>
-      </c>
+          <t>策星揽月</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
+          <t>412.5</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>412.5</t>
+        </is>
+      </c>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
@@ -6209,42 +5945,42 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
+          <t>920116_星图测控</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2017-10-25</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
+          <t>幸福一期</t>
         </is>
       </c>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>917.4219</t>
         </is>
       </c>
       <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>917.4219</t>
         </is>
       </c>
       <c r="J128" t="inlineStr"/>
@@ -6262,35 +5998,35 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
+          <t>920116_星图测控</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2017-10-25</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
+          <t>策星九天</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>2345.0781</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>2345.0781</t>
         </is>
       </c>
       <c r="J129" t="inlineStr"/>
@@ -6308,37 +6044,33 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
+          <t>920116_星图测控</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2017-10-25</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
+          <t>吴功友</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
-      <c r="F130" t="inlineStr"/>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>51.959</t>
-        </is>
-      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>51.959</t>
-        </is>
-      </c>
+      <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
@@ -6347,42 +6079,42 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
+          <t>920116_星图测控</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2017-10-25</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
+          <t>策星逐日</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="J131" t="inlineStr"/>
@@ -6400,35 +6132,35 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
+          <t>920116_星图测控</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2017-10-25</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
+          <t>中科星图股份有限公司</t>
         </is>
       </c>
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>3825.0</t>
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>3825.0</t>
         </is>
       </c>
       <c r="J132" t="inlineStr"/>
@@ -6446,46 +6178,42 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>7000.0</t>
-        </is>
-      </c>
+          <t>中科星图股份有限公司 (认缴→存量)</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>3825.0</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>1680.0</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>3825.0</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K133" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6493,45 +6221,49 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>上海联炻企业管理中心(有限合伙)</t>
+          <t>策星九天 (认缴→存量)</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
-          <t>297.3333</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr"/>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>2345.0781</t>
+        </is>
+      </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>297.3333</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr"/>
+          <t>2345.0781</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K134" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6539,45 +6271,49 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
+          <t>920116_星图测控</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
+          <t>幸福一期 (认缴→存量)</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
-          <t>29.7333</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr"/>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>917.4219</t>
+        </is>
+      </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>29.7333</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr"/>
+          <t>917.4219</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="K135" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6585,42 +6321,42 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>认购数 vs 存量持股数</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
+          <t>920116_星图测控</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司 (认缴→存量)</t>
+          <t>策星揽月 (认缴→存量)</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
-          <t>8976.0</t>
+          <t>412.5</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>8976.0</t>
+          <t>412.5</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>8976.0</t>
+          <t>412.5</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -6642,35 +6378,35 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
+          <t>920116_星图测控</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
+          <t>幸福二期 (认缴→存量)</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>300.0</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>300.0</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>300.0</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -6692,35 +6428,35 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
+          <t>920116_星图测控</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙) (认缴→存量)</t>
+          <t>策星银河 (认缴→存量)</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
-          <t>1020.0</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>1020.0</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>1020.0</t>
+          <t>279.0</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -6742,35 +6478,35 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
+          <t>920116_星图测控</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>罗世兵 (认缴→存量)</t>
+          <t>策星逐日 (认缴→存量)</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -6789,2932 +6525,24 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr"/>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr"/>
-      <c r="F140" t="inlineStr"/>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>840.0</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L140" t="inlineStr">
-        <is>
-          <t>认购数 vs 存量持股数</t>
-        </is>
-      </c>
-    </row>
     <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr"/>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr"/>
-      <c r="F141" t="inlineStr"/>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L141" t="inlineStr">
-        <is>
-          <t>认购数 vs 存量持股数</t>
+      <c r="A141" s="3" t="inlineStr">
+        <is>
+          <t>认缴流量: 12 条</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr"/>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>上海骁墨信息技术服务中心(有限合伙) (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr"/>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L142" t="inlineStr">
-        <is>
-          <t>认购数 vs 存量持股数</t>
+      <c r="A142" s="3" t="inlineStr">
+        <is>
+          <t>股权存量: 12 条</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr"/>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>深圳市杉晖创业投资合伙企业(有限合伙) (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr"/>
-      <c r="F143" t="inlineStr"/>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>297.3333</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>297.3333</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>297.3333</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L143" t="inlineStr">
-        <is>
-          <t>认购数 vs 存量持股数</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr"/>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>上海联炻企业管理中心(有限合伙) (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr"/>
-      <c r="F144" t="inlineStr"/>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>297.3333</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>297.3333</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>297.3333</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L144" t="inlineStr">
-        <is>
-          <t>认购数 vs 存量持股数</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr"/>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>安吉璞颉企业管理合伙企业(有限合伙) (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr"/>
-      <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>148.6667</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>148.6667</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>148.6667</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L145" t="inlineStr">
-        <is>
-          <t>认购数 vs 存量持股数</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr"/>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>江西赣江新区财投晨源股权投资中心(有限合伙) (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr"/>
-      <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>89.2</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>89.2</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>89.2</t>
-        </is>
-      </c>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L146" t="inlineStr">
-        <is>
-          <t>认购数 vs 存量持股数</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr"/>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>深圳市达晨创程私募股权投资基金企业(有限合伙) (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr"/>
-      <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>86.5984</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>86.5984</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>86.5984</t>
-        </is>
-      </c>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L147" t="inlineStr">
-        <is>
-          <t>认购数 vs 存量持股数</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr"/>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>上海杉创智至创业投资合伙企业(有限合伙) (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr"/>
-      <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>59.4667</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>59.4667</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>59.4667</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L148" t="inlineStr">
-        <is>
-          <t>认购数 vs 存量持股数</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr"/>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>杭州达晨创程股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr"/>
-      <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>51.959</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>51.959</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>51.959</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L149" t="inlineStr">
-        <is>
-          <t>认购数 vs 存量持股数</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr"/>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙) (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr"/>
-      <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>29.7333</t>
-        </is>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>29.7333</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>29.7333</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L150" t="inlineStr">
-        <is>
-          <t>认购数 vs 存量持股数</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr"/>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>深圳市达晨财智创业投资管理有限公司 (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr"/>
-      <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>29.7333</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>29.7333</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>29.7333</t>
-        </is>
-      </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L151" t="inlineStr">
-        <is>
-          <t>认购数 vs 存量持股数</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>603418_友升股份</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr"/>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>2022-12-19</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>深圳市财智创赢私募股权投资企业(有限合伙) (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr"/>
-      <c r="F152" t="inlineStr"/>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>10.1093</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>10.1093</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>10.1093</t>
-        </is>
-      </c>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L152" t="inlineStr">
-        <is>
-          <t>认购数 vs 存量持股数</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>2021-09-16</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>高新同华</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr"/>
-      <c r="F153" t="inlineStr"/>
-      <c r="G153" t="inlineStr"/>
-      <c r="H153" t="inlineStr"/>
-      <c r="I153" t="inlineStr"/>
-      <c r="J153" t="inlineStr"/>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L153" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>2021-09-16</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>周乃鼎</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr"/>
-      <c r="F154" t="inlineStr"/>
-      <c r="G154" t="inlineStr"/>
-      <c r="H154" t="inlineStr"/>
-      <c r="I154" t="inlineStr"/>
-      <c r="J154" t="inlineStr"/>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L154" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>2021-09-16</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>Cheer Rise Consultants Limited</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr"/>
-      <c r="F155" t="inlineStr"/>
-      <c r="G155" t="inlineStr"/>
-      <c r="H155" t="inlineStr"/>
-      <c r="I155" t="inlineStr"/>
-      <c r="J155" t="inlineStr"/>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L155" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>2021-09-16</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>陆民</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr"/>
-      <c r="F156" t="inlineStr"/>
-      <c r="G156" t="inlineStr"/>
-      <c r="H156" t="inlineStr"/>
-      <c r="I156" t="inlineStr"/>
-      <c r="J156" t="inlineStr"/>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L156" t="inlineStr"/>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>2021-09-16</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>黄学英</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr"/>
-      <c r="F157" t="inlineStr"/>
-      <c r="G157" t="inlineStr"/>
-      <c r="H157" t="inlineStr"/>
-      <c r="I157" t="inlineStr"/>
-      <c r="J157" t="inlineStr"/>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L157" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>2021-09-16</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>周金清</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr"/>
-      <c r="F158" t="inlineStr"/>
-      <c r="G158" t="inlineStr"/>
-      <c r="H158" t="inlineStr"/>
-      <c r="I158" t="inlineStr"/>
-      <c r="J158" t="inlineStr"/>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L158" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>2021-09-16</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>苏州贤达</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr"/>
-      <c r="F159" t="inlineStr"/>
-      <c r="G159" t="inlineStr"/>
-      <c r="H159" t="inlineStr"/>
-      <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L159" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>2021-09-16</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>国寿疌泉</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr"/>
-      <c r="F160" t="inlineStr"/>
-      <c r="G160" t="inlineStr"/>
-      <c r="H160" t="inlineStr"/>
-      <c r="I160" t="inlineStr"/>
-      <c r="J160" t="inlineStr"/>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L160" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>2021-09-16</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>黄学英/刘鸿雁</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr"/>
-      <c r="F161" t="inlineStr"/>
-      <c r="G161" t="inlineStr"/>
-      <c r="H161" t="inlineStr"/>
-      <c r="I161" t="inlineStr"/>
-      <c r="J161" t="inlineStr"/>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L161" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>2021-09-16</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>复星惟盈</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr"/>
-      <c r="F162" t="inlineStr"/>
-      <c r="G162" t="inlineStr"/>
-      <c r="H162" t="inlineStr"/>
-      <c r="I162" t="inlineStr"/>
-      <c r="J162" t="inlineStr"/>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L162" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>2021-09-16</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>史建伟</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr"/>
-      <c r="F163" t="inlineStr"/>
-      <c r="G163" t="inlineStr"/>
-      <c r="H163" t="inlineStr"/>
-      <c r="I163" t="inlineStr"/>
-      <c r="J163" t="inlineStr"/>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L163" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>688758_赛分科技</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>2011-10</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>2021-09-16</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>华泰大健康一号</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr"/>
-      <c r="F164" t="inlineStr"/>
-      <c r="G164" t="inlineStr"/>
-      <c r="H164" t="inlineStr"/>
-      <c r="I164" t="inlineStr"/>
-      <c r="J164" t="inlineStr"/>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L164" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>2015-07-09</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>深圳中证投资有限责任公司</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr"/>
-      <c r="F165" t="inlineStr"/>
-      <c r="G165" t="inlineStr"/>
-      <c r="H165" t="inlineStr"/>
-      <c r="I165" t="inlineStr"/>
-      <c r="J165" t="inlineStr"/>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L165" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>2015-07-09</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr"/>
-      <c r="F166" t="inlineStr"/>
-      <c r="G166" t="inlineStr"/>
-      <c r="H166" t="inlineStr"/>
-      <c r="I166" t="inlineStr"/>
-      <c r="J166" t="inlineStr"/>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L166" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>2015-07-09</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>北京岚锋创视网络科技有限公司</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr"/>
-      <c r="F167" t="inlineStr"/>
-      <c r="G167" t="inlineStr"/>
-      <c r="H167" t="inlineStr"/>
-      <c r="I167" t="inlineStr"/>
-      <c r="J167" t="inlineStr"/>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L167" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>2015-07-09</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>香港迅雷有限公司</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr"/>
-      <c r="F168" t="inlineStr"/>
-      <c r="G168" t="inlineStr"/>
-      <c r="H168" t="inlineStr"/>
-      <c r="I168" t="inlineStr"/>
-      <c r="J168" t="inlineStr"/>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L168" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>2015-07-09</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>厦门富凯海创投资管理有限责任公司</t>
-        </is>
-      </c>
-      <c r="E169" t="inlineStr"/>
-      <c r="F169" t="inlineStr"/>
-      <c r="G169" t="inlineStr"/>
-      <c r="H169" t="inlineStr"/>
-      <c r="I169" t="inlineStr"/>
-      <c r="J169" t="inlineStr"/>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L169" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>2015-07-09</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr"/>
-      <c r="F170" t="inlineStr"/>
-      <c r="G170" t="inlineStr"/>
-      <c r="H170" t="inlineStr"/>
-      <c r="I170" t="inlineStr"/>
-      <c r="J170" t="inlineStr"/>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L170" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>2015-07-09</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>QM101 Limited</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr"/>
-      <c r="F171" t="inlineStr"/>
-      <c r="G171" t="inlineStr"/>
-      <c r="H171" t="inlineStr"/>
-      <c r="I171" t="inlineStr"/>
-      <c r="J171" t="inlineStr"/>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L171" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>2015-07-09</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>深圳市伊敦传媒投资基金合伙企业（有限合伙）</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr"/>
-      <c r="F172" t="inlineStr"/>
-      <c r="G172" t="inlineStr"/>
-      <c r="H172" t="inlineStr"/>
-      <c r="I172" t="inlineStr"/>
-      <c r="J172" t="inlineStr"/>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L172" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>2015-01</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>2015-07-09</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>EARN ACE LIMITED</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr"/>
-      <c r="F173" t="inlineStr"/>
-      <c r="G173" t="inlineStr"/>
-      <c r="H173" t="inlineStr"/>
-      <c r="I173" t="inlineStr"/>
-      <c r="J173" t="inlineStr"/>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L173" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>2015-07-09</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>2020-02-26</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>香港迅雷有限公司</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr"/>
-      <c r="F174" t="inlineStr"/>
-      <c r="G174" t="inlineStr"/>
-      <c r="H174" t="inlineStr"/>
-      <c r="I174" t="inlineStr"/>
-      <c r="J174" t="inlineStr"/>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L174" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>2015-07-09</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>2020-02-26</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>北京岚锋创视网络科技有限公司</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr"/>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr"/>
-      <c r="H175" t="inlineStr"/>
-      <c r="I175" t="inlineStr"/>
-      <c r="J175" t="inlineStr"/>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L175" t="inlineStr"/>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>2015-07-09</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>2020-02-26</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>QM101 Limited</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr"/>
-      <c r="F176" t="inlineStr"/>
-      <c r="G176" t="inlineStr"/>
-      <c r="H176" t="inlineStr"/>
-      <c r="I176" t="inlineStr"/>
-      <c r="J176" t="inlineStr"/>
-      <c r="K176" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L176" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>2015-07-09</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>2020-02-26</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>EARN ACE LIMITED</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr"/>
-      <c r="F177" t="inlineStr"/>
-      <c r="G177" t="inlineStr"/>
-      <c r="H177" t="inlineStr"/>
-      <c r="I177" t="inlineStr"/>
-      <c r="J177" t="inlineStr"/>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L177" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>2020-02-26</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>2023-03-24</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>香港迅雷有限公司</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr"/>
-      <c r="F178" t="inlineStr"/>
-      <c r="G178" t="inlineStr"/>
-      <c r="H178" t="inlineStr"/>
-      <c r="I178" t="inlineStr"/>
-      <c r="J178" t="inlineStr"/>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L178" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>2020-02-26</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>2023-03-24</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>北京岚锋创视网络科技有限公司</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr"/>
-      <c r="F179" t="inlineStr"/>
-      <c r="G179" t="inlineStr"/>
-      <c r="H179" t="inlineStr"/>
-      <c r="I179" t="inlineStr"/>
-      <c r="J179" t="inlineStr"/>
-      <c r="K179" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L179" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>2020-02-26</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>2023-03-24</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>汇智同裕（深圳）投资合伙企业（有限合伙）</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr"/>
-      <c r="F180" t="inlineStr"/>
-      <c r="G180" t="inlineStr"/>
-      <c r="H180" t="inlineStr"/>
-      <c r="I180" t="inlineStr"/>
-      <c r="J180" t="inlineStr"/>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L180" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>2020-02-26</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>2023-03-24</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>QM101 Limited</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr"/>
-      <c r="F181" t="inlineStr"/>
-      <c r="G181" t="inlineStr"/>
-      <c r="H181" t="inlineStr"/>
-      <c r="I181" t="inlineStr"/>
-      <c r="J181" t="inlineStr"/>
-      <c r="K181" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L181" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>688775_影石创新</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>2020-02-26</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>2023-03-24</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>EARN ACE LIMITED</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr"/>
-      <c r="F182" t="inlineStr"/>
-      <c r="G182" t="inlineStr"/>
-      <c r="H182" t="inlineStr"/>
-      <c r="I182" t="inlineStr"/>
-      <c r="J182" t="inlineStr"/>
-      <c r="K182" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L182" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>920100_三协电机</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr"/>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>2023-09-06</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>盛祎等15名自然人</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr"/>
-      <c r="F183" t="inlineStr"/>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>321.5</t>
-        </is>
-      </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>1739.315</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>1723.09</t>
-        </is>
-      </c>
-      <c r="J183" t="inlineStr">
-        <is>
-          <t>16.225</t>
-        </is>
-      </c>
-      <c r="K183" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L183" t="inlineStr">
-        <is>
-          <t>price×shares vs amount diff=0.9%</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>920100_三协电机</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>2002-11-07</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>2022-08-09</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>朱绶青</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr"/>
-      <c r="F184" t="inlineStr"/>
-      <c r="G184" t="inlineStr"/>
-      <c r="H184" t="inlineStr"/>
-      <c r="I184" t="inlineStr"/>
-      <c r="J184" t="inlineStr"/>
-      <c r="K184" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L184" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>920100_三协电机</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>2002-11-07</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>2022-08-09</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr"/>
-      <c r="F185" t="inlineStr"/>
-      <c r="G185" t="inlineStr"/>
-      <c r="H185" t="inlineStr"/>
-      <c r="I185" t="inlineStr"/>
-      <c r="J185" t="inlineStr"/>
-      <c r="K185" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L185" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>920100_三协电机</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>2002-11-07</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>2022-08-09</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>盛祎</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr"/>
-      <c r="F186" t="inlineStr"/>
-      <c r="G186" t="inlineStr"/>
-      <c r="H186" t="inlineStr"/>
-      <c r="I186" t="inlineStr"/>
-      <c r="J186" t="inlineStr"/>
-      <c r="K186" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L186" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>2016-12-14</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>2017-10-25</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>牛威(罗永红代持)</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr"/>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>400.0</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr"/>
-      <c r="H187" t="inlineStr"/>
-      <c r="I187" t="inlineStr"/>
-      <c r="J187" t="inlineStr"/>
-      <c r="K187" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L187" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>2016-12-14</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>2017-10-25</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>吴功友(王金林代持)</t>
-        </is>
-      </c>
-      <c r="E188" t="inlineStr"/>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>400.0</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr"/>
-      <c r="H188" t="inlineStr"/>
-      <c r="I188" t="inlineStr"/>
-      <c r="J188" t="inlineStr"/>
-      <c r="K188" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L188" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>2016-12-14</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>2017-10-25</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>四方股份</t>
-        </is>
-      </c>
-      <c r="E189" t="inlineStr"/>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>1200.0</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr"/>
-      <c r="H189" t="inlineStr"/>
-      <c r="I189" t="inlineStr"/>
-      <c r="J189" t="inlineStr"/>
-      <c r="K189" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L189" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>2016-12-14</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>2017-10-25</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>牛威</t>
-        </is>
-      </c>
-      <c r="E190" t="inlineStr"/>
-      <c r="F190" t="inlineStr"/>
-      <c r="G190" t="inlineStr"/>
-      <c r="H190" t="inlineStr"/>
-      <c r="I190" t="inlineStr"/>
-      <c r="J190" t="inlineStr"/>
-      <c r="K190" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L190" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>2016-12-14</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>2017-10-25</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>吴功友</t>
-        </is>
-      </c>
-      <c r="E191" t="inlineStr"/>
-      <c r="F191" t="inlineStr"/>
-      <c r="G191" t="inlineStr"/>
-      <c r="H191" t="inlineStr"/>
-      <c r="I191" t="inlineStr"/>
-      <c r="J191" t="inlineStr"/>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L191" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>2017-10-25</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>幸福二期</t>
-        </is>
-      </c>
-      <c r="E192" t="inlineStr"/>
-      <c r="F192" t="inlineStr"/>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>300.0</t>
-        </is>
-      </c>
-      <c r="H192" t="inlineStr"/>
-      <c r="I192" t="inlineStr">
-        <is>
-          <t>300.0</t>
-        </is>
-      </c>
-      <c r="J192" t="inlineStr"/>
-      <c r="K192" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L192" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>2017-10-25</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>策星银河</t>
-        </is>
-      </c>
-      <c r="E193" t="inlineStr"/>
-      <c r="F193" t="inlineStr"/>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
-      <c r="H193" t="inlineStr"/>
-      <c r="I193" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
-      <c r="J193" t="inlineStr"/>
-      <c r="K193" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L193" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>2017-10-25</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>策星逐日</t>
-        </is>
-      </c>
-      <c r="E194" t="inlineStr"/>
-      <c r="F194" t="inlineStr"/>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>171.0</t>
-        </is>
-      </c>
-      <c r="H194" t="inlineStr"/>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>171.0</t>
-        </is>
-      </c>
-      <c r="J194" t="inlineStr"/>
-      <c r="K194" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L194" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>2017-10-25</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>策星揽月</t>
-        </is>
-      </c>
-      <c r="E195" t="inlineStr"/>
-      <c r="F195" t="inlineStr"/>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>412.5</t>
-        </is>
-      </c>
-      <c r="H195" t="inlineStr"/>
-      <c r="I195" t="inlineStr">
-        <is>
-          <t>412.5</t>
-        </is>
-      </c>
-      <c r="J195" t="inlineStr"/>
-      <c r="K195" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L195" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>2017-10-25</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>牛威</t>
-        </is>
-      </c>
-      <c r="E196" t="inlineStr"/>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G196" t="inlineStr"/>
-      <c r="H196" t="inlineStr"/>
-      <c r="I196" t="inlineStr"/>
-      <c r="J196" t="inlineStr"/>
-      <c r="K196" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L196" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>2017-10-25</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>幸福一期</t>
-        </is>
-      </c>
-      <c r="E197" t="inlineStr"/>
-      <c r="F197" t="inlineStr"/>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>917.4219</t>
-        </is>
-      </c>
-      <c r="H197" t="inlineStr"/>
-      <c r="I197" t="inlineStr">
-        <is>
-          <t>917.4219</t>
-        </is>
-      </c>
-      <c r="J197" t="inlineStr"/>
-      <c r="K197" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L197" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>2017-10-25</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>策星九天</t>
-        </is>
-      </c>
-      <c r="E198" t="inlineStr"/>
-      <c r="F198" t="inlineStr"/>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
-      <c r="H198" t="inlineStr"/>
-      <c r="I198" t="inlineStr">
-        <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
-      <c r="J198" t="inlineStr"/>
-      <c r="K198" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L198" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>2017-10-25</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>中科星图股份有限公司</t>
-        </is>
-      </c>
-      <c r="E199" t="inlineStr"/>
-      <c r="F199" t="inlineStr"/>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>3825.0</t>
-        </is>
-      </c>
-      <c r="H199" t="inlineStr"/>
-      <c r="I199" t="inlineStr">
-        <is>
-          <t>3825.0</t>
-        </is>
-      </c>
-      <c r="J199" t="inlineStr"/>
-      <c r="K199" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L199" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>2017-10-25</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>吴功友</t>
-        </is>
-      </c>
-      <c r="E200" t="inlineStr"/>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G200" t="inlineStr"/>
-      <c r="H200" t="inlineStr"/>
-      <c r="I200" t="inlineStr"/>
-      <c r="J200" t="inlineStr"/>
-      <c r="K200" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L200" t="inlineStr">
-        <is>
-          <t>退出</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr"/>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>中科星图股份有限公司 (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E201" t="inlineStr"/>
-      <c r="F201" t="inlineStr"/>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>3825.0</t>
-        </is>
-      </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>3825.0</t>
-        </is>
-      </c>
-      <c r="I201" t="inlineStr">
-        <is>
-          <t>3825.0</t>
-        </is>
-      </c>
-      <c r="J201" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L201" t="inlineStr">
-        <is>
-          <t>认购数 vs 存量持股数</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr"/>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>策星九天 (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E202" t="inlineStr"/>
-      <c r="F202" t="inlineStr"/>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr">
-        <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
-      <c r="J202" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="K202" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L202" t="inlineStr">
-        <is>
-          <t>认购数 vs 存量持股数</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr"/>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>幸福一期 (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E203" t="inlineStr"/>
-      <c r="F203" t="inlineStr"/>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>917.4219</t>
-        </is>
-      </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>917.4219</t>
-        </is>
-      </c>
-      <c r="I203" t="inlineStr">
-        <is>
-          <t>917.4219</t>
-        </is>
-      </c>
-      <c r="J203" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="K203" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L203" t="inlineStr">
-        <is>
-          <t>认购数 vs 存量持股数</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr"/>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>策星揽月 (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E204" t="inlineStr"/>
-      <c r="F204" t="inlineStr"/>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>412.5</t>
-        </is>
-      </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>412.5</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr">
-        <is>
-          <t>412.5</t>
-        </is>
-      </c>
-      <c r="J204" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="K204" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L204" t="inlineStr">
-        <is>
-          <t>认购数 vs 存量持股数</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr"/>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>幸福二期 (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E205" t="inlineStr"/>
-      <c r="F205" t="inlineStr"/>
-      <c r="G205" t="inlineStr">
-        <is>
-          <t>300.0</t>
-        </is>
-      </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>300.0</t>
-        </is>
-      </c>
-      <c r="I205" t="inlineStr">
-        <is>
-          <t>300.0</t>
-        </is>
-      </c>
-      <c r="J205" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="K205" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L205" t="inlineStr">
-        <is>
-          <t>认购数 vs 存量持股数</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr"/>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>策星银河 (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E206" t="inlineStr"/>
-      <c r="F206" t="inlineStr"/>
-      <c r="G206" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
-      <c r="I206" t="inlineStr">
-        <is>
-          <t>279.0</t>
-        </is>
-      </c>
-      <c r="J206" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="K206" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L206" t="inlineStr">
-        <is>
-          <t>认购数 vs 存量持股数</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>920116_星图测控</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr"/>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>2024-06-30</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>策星逐日 (认缴→存量)</t>
-        </is>
-      </c>
-      <c r="E207" t="inlineStr"/>
-      <c r="F207" t="inlineStr"/>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>171.0</t>
-        </is>
-      </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>171.0</t>
-        </is>
-      </c>
-      <c r="I207" t="inlineStr">
-        <is>
-          <t>171.0</t>
-        </is>
-      </c>
-      <c r="J207" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="K207" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="L207" t="inlineStr">
-        <is>
-          <t>认购数 vs 存量持股数</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" s="3" t="inlineStr">
-        <is>
-          <t>认缴流量: 12 条</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" s="3" t="inlineStr">
-        <is>
-          <t>股权存量: 12 条</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>生成时间: 2026-06-12T16:30:01.235495</t>
+          <t>生成时间: 2026-06-12T17:00:58.890890</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/920116_星图测控_三表抽取.xlsx
+++ b/outputs/week2_excel/920116_星图测控_三表抽取.xlsx
@@ -2379,11 +2379,15 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>深圳市云汉电子有限公司</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
@@ -2395,7 +2399,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2455,15 +2459,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -2535,7 +2535,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>深圳市云汉电子有限公司</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>东方富海（上海）创业投资企业（有限合伙）</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2615,7 +2615,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>东方富海（上海）创业投资企业（有限合伙）</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -2631,7 +2631,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>芜湖富海浩研创业投资基金（有限合伙）</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
@@ -2745,7 +2745,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -2881,7 +2881,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>武汉力源信息技术股份有限公司</t>
+          <t>深圳市创新投资集团有限公司</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -2897,7 +2897,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -2957,11 +2957,15 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>深圳市创新投资集团有限公司</t>
+          <t>丰利财富（北京）国际资本管理股份有限公司</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
@@ -2995,7 +2999,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>昆山红土高新创业投资有限公司</t>
+          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -3033,15 +3037,11 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>丰利财富（北京）国际资本管理股份有限公司</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>1000.0</t>
-        </is>
-      </c>
+      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>武汉力源信息技术股份有限公司</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
@@ -3113,7 +3113,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>镇江红土创业投资有限公司</t>
+          <t>昆山红土高新创业投资有限公司</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>富海深湾（深圳）移动创新私募创业投资基金合伙企业（有限合伙）</t>
+          <t>镇江红土创业投资有限公司</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
@@ -3357,7 +3357,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3379,7 +3379,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -3417,7 +3417,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -3493,7 +3493,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -3531,13 +3531,13 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>204.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -3573,11 +3573,15 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>火炬电子科技股份有限公司</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
@@ -3589,7 +3593,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -3611,13 +3615,13 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>珠海拓域投资合伙企业（有限合伙）</t>
+          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>1000.0</t>
+          <t>1584.0</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -3653,13 +3657,13 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>中科贵银（贵州）创业投资中心（有限合伙）</t>
+          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1584.0</t>
+          <t>7412.0</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -3695,13 +3699,13 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>珠海拓域投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1800.0</t>
+          <t>1000.0</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
@@ -3737,13 +3741,13 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>深圳南山富海中小企业发展基金合伙企业（有限合伙）</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>204.0</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -3779,15 +3783,11 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>国科瑞华（北京）创业投资合伙企业（有限合伙）</t>
+          <t>火炬电子科技股份有限公司</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>7412.0</t>
-        </is>
-      </c>
+      <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>厦门西堤股权投资合伙企业（有限合伙）</t>
+          <t>中小企业发展基金（深圳有限合伙）</t>
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
@@ -3901,7 +3901,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>中小企业发展基金（深圳有限合伙）</t>
+          <t>厦门西堤股权投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
@@ -3939,7 +3939,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
@@ -4057,7 +4057,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
@@ -4129,7 +4129,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -4163,7 +4163,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
@@ -4197,7 +4197,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -4213,7 +4213,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4273,7 +4273,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
@@ -4289,7 +4289,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4311,7 +4311,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -4349,7 +4349,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
@@ -4387,15 +4387,11 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>黄山佳捷股权管理中心（有限合伙）</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>10377.0</t>
-        </is>
-      </c>
+      <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
@@ -4407,7 +4403,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -4429,11 +4425,15 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>黄山佳捷股权管理中心（有限合伙）</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>10377.0</t>
+        </is>
+      </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
@@ -4445,7 +4445,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -4547,7 +4547,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>张俊武</t>
+          <t>上海广弘实业有限公司</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
@@ -4623,7 +4623,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>上海广弘实业有限公司</t>
+          <t>张俊武</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
@@ -4661,7 +4661,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>黄山供销集团有限公司</t>
+          <t>周斌</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
@@ -4699,7 +4699,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>周斌</t>
+          <t>黄山供销集团有限公司</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -5387,14 +5387,22 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>上海市青浦县徐泾乡工业公司</t>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
@@ -5403,7 +5411,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5425,22 +5433,14 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+          <t>友升太平洋(美国)投资有限公司</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+      <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
@@ -5449,7 +5449,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5471,22 +5471,14 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
+          <t>上海市青浦县徐泾乡工业公司</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+      <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>8976.0</t>
-        </is>
-      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
@@ -5495,7 +5487,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5517,20 +5509,20 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
+          <t>上海泽升贸易有限公司</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>1020.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr">
         <is>
-          <t>1020.0</t>
+          <t>8976.0</t>
         </is>
       </c>
       <c r="J113" t="inlineStr"/>
@@ -5563,14 +5555,22 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>友升太平洋(美国)投资有限公司</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr"/>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr"/>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>1020.0</t>
+        </is>
+      </c>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5647,20 +5647,20 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="J116" t="inlineStr"/>
@@ -5693,22 +5693,26 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr"/>
+          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>1800.0</t>
+        </is>
+      </c>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
+          <t>1800.0</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>3600.0</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr">
         <is>
@@ -5717,7 +5721,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5739,26 +5743,22 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>深圳市达晨创联私募股权投资基金合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>1800.0</t>
-        </is>
-      </c>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>1800.0</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>3600.0</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>840.0</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>840.0</t>
+        </is>
+      </c>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
         <is>
@@ -5767,7 +5767,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5789,22 +5789,26 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr"/>
+          <t>上海泽升贸易有限公司</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>8976.0</t>
+        </is>
+      </c>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
+          <t>8976.0</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>17952.0</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
@@ -5813,7 +5817,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -5835,23 +5839,23 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>上海泽升贸易有限公司</t>
+          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>8976.0</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>8976.0</t>
+          <t>1020.0</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>17952.0</t>
+          <t>2040.0</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -5885,26 +5889,22 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>共青城泽升投资管理合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>1020.0</t>
-        </is>
-      </c>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>1020.0</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>2040.0</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -5985,20 +5985,20 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>深圳市达晨财智创业投资管理有限公司</t>
+          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>10.1093</t>
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>10.1093</t>
         </is>
       </c>
       <c r="J123" t="inlineStr"/>
@@ -6031,20 +6031,20 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
+          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>86.5984</t>
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>86.5984</t>
         </is>
       </c>
       <c r="J124" t="inlineStr"/>
@@ -6077,20 +6077,20 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>上海联炻企业管理中心(有限合伙)</t>
+          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>59.4667</t>
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>59.4667</t>
         </is>
       </c>
       <c r="J125" t="inlineStr"/>
@@ -6123,20 +6123,20 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
+          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>51.959</t>
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr">
         <is>
-          <t>29.7333</t>
+          <t>51.959</t>
         </is>
       </c>
       <c r="J126" t="inlineStr"/>
@@ -6169,30 +6169,22 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>上海骁墨信息技术服务中心(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>1500.0</t>
-        </is>
-      </c>
+          <t>深圳市达晨财智创业投资管理有限公司</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
-          <t>180.0</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>360.0</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
+          <t>29.7333</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>29.7333</t>
+        </is>
+      </c>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
@@ -6201,7 +6193,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -6223,27 +6215,27 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
+          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>7000.0</t>
+          <t>3000.0</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>840.0</t>
+          <t>360.0</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>1680.0</t>
+          <t>720.0</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -6277,20 +6269,20 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
+          <t>上海联炻企业管理中心(有限合伙)</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
-          <t>148.6667</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J129" t="inlineStr"/>
@@ -6323,22 +6315,30 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>上海杉创智至创业投资合伙企业(有限合伙)</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr"/>
-      <c r="F130" t="inlineStr"/>
+          <t>上海骁墨信息技术服务中心(有限合伙)</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>1500.0</t>
+        </is>
+      </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>59.4667</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>59.4667</t>
-        </is>
-      </c>
+          <t>180.0</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>360.0</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
@@ -6347,7 +6347,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -6369,20 +6369,20 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>深圳市财智创赢私募股权投资企业(有限合伙)</t>
+          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
-          <t>10.1093</t>
+          <t>297.3333</t>
         </is>
       </c>
       <c r="J131" t="inlineStr"/>
@@ -6415,27 +6415,27 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>上海金浦科技创业股权投资基金合伙企业(有限合伙)</t>
+          <t>上海金浦临港智能科技股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>360.0</t>
+          <t>840.0</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>3000.0</t>
+          <t>7000.0</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>360.0</t>
+          <t>840.0</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>720.0</t>
+          <t>1680.0</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -6469,20 +6469,20 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>深圳市杉晖创业投资合伙企业(有限合伙)</t>
+          <t>安吉璞颉企业管理合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>148.6667</t>
         </is>
       </c>
       <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr">
         <is>
-          <t>297.3333</t>
+          <t>148.6667</t>
         </is>
       </c>
       <c r="J133" t="inlineStr"/>
@@ -6515,20 +6515,20 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>深圳市达晨创程私募股权投资基金企业(有限合伙)</t>
+          <t>海南三亚达晨财汇私募股权投资基金合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
-          <t>86.5984</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
-          <t>86.5984</t>
+          <t>29.7333</t>
         </is>
       </c>
       <c r="J134" t="inlineStr"/>
@@ -6561,20 +6561,20 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>杭州达晨创程股权投资基金合伙企业(有限合伙)</t>
+          <t>江西赣江新区财投晨源股权投资中心(有限合伙)</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr">
         <is>
-          <t>51.959</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="J135" t="inlineStr"/>
@@ -7457,7 +7457,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>国寿疌泉</t>
+          <t>苏州贤达</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
@@ -7495,7 +7495,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Cheer Rise Consultants Limited</t>
+          <t>史建伟</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
@@ -7533,7 +7533,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>复星惟盈</t>
+          <t>黄学英/刘鸿雁</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
@@ -7549,7 +7549,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7571,7 +7571,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>苏州贤达</t>
+          <t>国寿疌泉</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
@@ -7609,7 +7609,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>黄学英</t>
+          <t>周乃鼎</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -7625,7 +7625,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -7647,7 +7647,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>史建伟</t>
+          <t>周金清</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -7663,7 +7663,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7685,7 +7685,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>周金清</t>
+          <t>复星惟盈</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -7723,7 +7723,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>周乃鼎</t>
+          <t>Cheer Rise Consultants Limited</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
@@ -7761,7 +7761,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>华泰大健康一号</t>
+          <t>陆民</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -7775,11 +7775,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L161" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
+      <c r="L161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -7799,7 +7795,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>高新同华</t>
+          <t>黄学英</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
@@ -7837,7 +7833,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>陆民</t>
+          <t>华泰大健康一号</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -7851,7 +7847,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="L163" t="inlineStr"/>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -7871,7 +7871,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>黄学英/刘鸿雁</t>
+          <t>高新同华</t>
         </is>
       </c>
       <c r="E164" t="inlineStr"/>
@@ -7887,7 +7887,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -7909,7 +7909,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>厦门富凯海创投资管理有限责任公司</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -7947,7 +7947,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>深圳中证投资有限责任公司</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E166" t="inlineStr"/>
@@ -7985,7 +7985,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
+          <t>深圳市伊敦传媒投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
@@ -8023,7 +8023,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
@@ -8061,7 +8061,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>北京岚锋创视网络科技有限公司</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
@@ -8077,7 +8077,7 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8099,7 +8099,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>深圳市伊敦传媒投资基金合伙企业（有限合伙）</t>
+          <t>北京岚锋创视网络科技有限公司</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8137,7 +8137,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
@@ -8175,7 +8175,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>金石智娱股权投资（深圳）合伙企业（有限合伙）</t>
+          <t>华金同达（深圳）投资合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
@@ -8213,7 +8213,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>厦门富凯海创投资管理有限责任公司</t>
+          <t>深圳中证投资有限责任公司</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
@@ -8251,7 +8251,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E174" t="inlineStr"/>
@@ -8289,7 +8289,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
@@ -8327,7 +8327,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>QM101 Limited</t>
+          <t>香港迅雷有限公司</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>EARN ACE LIMITED</t>
+          <t>QM101 Limited</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
@@ -8517,7 +8517,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>香港迅雷有限公司</t>
+          <t>EARN ACE LIMITED</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
@@ -8616,7 +8616,7 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>待复核</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -8643,7 +8643,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>盛祎</t>
+          <t>朱绶青</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
@@ -8681,7 +8681,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
+          <t>盛祎</t>
         </is>
       </c>
       <c r="E185" t="inlineStr"/>
@@ -8697,7 +8697,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8719,7 +8719,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>朱绶青</t>
+          <t>深圳市稳正景明创业投资企业(有限合伙)</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8757,13 +8757,13 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>四方股份</t>
+          <t>牛威(罗永红代持)</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr">
         <is>
-          <t>1200.0</t>
+          <t>400.0</t>
         </is>
       </c>
       <c r="G187" t="inlineStr"/>
@@ -8799,15 +8799,11 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>吴功友(王金林代持)</t>
+          <t>吴功友</t>
         </is>
       </c>
       <c r="E188" t="inlineStr"/>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>400.0</t>
-        </is>
-      </c>
+      <c r="F188" t="inlineStr"/>
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="inlineStr"/>
       <c r="I188" t="inlineStr"/>
@@ -8819,7 +8815,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -8879,11 +8875,15 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>吴功友</t>
+          <t>四方股份</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
-      <c r="F190" t="inlineStr"/>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>1200.0</t>
+        </is>
+      </c>
       <c r="G190" t="inlineStr"/>
       <c r="H190" t="inlineStr"/>
       <c r="I190" t="inlineStr"/>
@@ -8895,7 +8895,7 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -8917,7 +8917,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>牛威(罗永红代持)</t>
+          <t>吴功友(王金林代持)</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
@@ -8959,22 +8959,18 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>策星九天</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
-      <c r="F192" t="inlineStr"/>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr"/>
       <c r="H192" t="inlineStr"/>
-      <c r="I192" t="inlineStr">
-        <is>
-          <t>2345.0781</t>
-        </is>
-      </c>
+      <c r="I192" t="inlineStr"/>
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr">
         <is>
@@ -8983,7 +8979,7 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -9005,20 +9001,20 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>幸福二期</t>
+          <t>策星揽月</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr"/>
       <c r="G193" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>412.5</t>
         </is>
       </c>
       <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr">
         <is>
-          <t>300.0</t>
+          <t>412.5</t>
         </is>
       </c>
       <c r="J193" t="inlineStr"/>
@@ -9051,20 +9047,20 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>策星逐日</t>
+          <t>策星九天</t>
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr"/>
       <c r="G194" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>2345.0781</t>
         </is>
       </c>
       <c r="H194" t="inlineStr"/>
       <c r="I194" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>2345.0781</t>
         </is>
       </c>
       <c r="J194" t="inlineStr"/>
@@ -9097,18 +9093,22 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>幸福二期</t>
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G195" t="inlineStr"/>
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
       <c r="H195" t="inlineStr"/>
-      <c r="I195" t="inlineStr"/>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
       <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr">
         <is>
@@ -9117,7 +9117,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9139,18 +9139,22 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>吴功友</t>
+          <t>策星银河</t>
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G196" t="inlineStr"/>
+      <c r="F196" t="inlineStr"/>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
       <c r="H196" t="inlineStr"/>
-      <c r="I196" t="inlineStr"/>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>279.0</t>
+        </is>
+      </c>
       <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr">
         <is>
@@ -9159,7 +9163,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>新增</t>
         </is>
       </c>
     </row>
@@ -9181,22 +9185,18 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>中科星图股份有限公司</t>
+          <t>吴功友</t>
         </is>
       </c>
       <c r="E197" t="inlineStr"/>
-      <c r="F197" t="inlineStr"/>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>3825.0</t>
-        </is>
-      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr"/>
       <c r="H197" t="inlineStr"/>
-      <c r="I197" t="inlineStr">
-        <is>
-          <t>3825.0</t>
-        </is>
-      </c>
+      <c r="I197" t="inlineStr"/>
       <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr">
         <is>
@@ -9205,7 +9205,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -9227,20 +9227,20 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>幸福一期</t>
+          <t>中科星图股份有限公司</t>
         </is>
       </c>
       <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr"/>
       <c r="G198" t="inlineStr">
         <is>
-          <t>917.4219</t>
+          <t>3825.0</t>
         </is>
       </c>
       <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr">
         <is>
-          <t>917.4219</t>
+          <t>3825.0</t>
         </is>
       </c>
       <c r="J198" t="inlineStr"/>
@@ -9273,20 +9273,20 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>策星揽月</t>
+          <t>幸福一期</t>
         </is>
       </c>
       <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr"/>
       <c r="G199" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>917.4219</t>
         </is>
       </c>
       <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr">
         <is>
-          <t>412.5</t>
+          <t>917.4219</t>
         </is>
       </c>
       <c r="J199" t="inlineStr"/>
@@ -9319,20 +9319,20 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>策星银河</t>
+          <t>策星逐日</t>
         </is>
       </c>
       <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr"/>
       <c r="G200" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="H200" t="inlineStr"/>
       <c r="I200" t="inlineStr">
         <is>
-          <t>279.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="J200" t="inlineStr"/>
@@ -9714,7 +9714,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>生成时间: 2026-06-12T17:05:42.776363</t>
+          <t>生成时间: 2026-06-12T17:10:43.487104</t>
         </is>
       </c>
     </row>
